--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molt246-my.sharepoint.com/personal/lauras_molt_com_co/Documents/Documentos/GitHub/Costo mano de obra/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_621513AAD340D14033B93811595ED87656C45730" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7867F3C6-5FED-4FF5-852F-78291AB56C1D}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_621513AAD340D14033B93811595ED87656C45730" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86AED7E8-EA37-408A-8939-CE0CE0C4F186}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4482,10 +4482,7 @@
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
@@ -4503,7 +4500,10 @@
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
@@ -4574,33 +4574,33 @@
     <tableColumn id="2" xr3:uid="{4464ACF8-DA19-4EF8-AC52-7CF4992D4D02}" name="Secuencia"/>
     <tableColumn id="3" xr3:uid="{94B79CF7-5ECA-4CA2-B217-05597A002186}" name="OP Det"/>
     <tableColumn id="4" xr3:uid="{24E2E3AE-172D-45A4-9E3A-E02355BF2F22}" name="Producir"/>
-    <tableColumn id="5" xr3:uid="{BFCD1E38-F11A-488C-AF8E-10D708BB2794}" name="Creado El" dataDxfId="14" totalsRowDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{BFCD1E38-F11A-488C-AF8E-10D708BB2794}" name="Creado El" dataDxfId="14" totalsRowDxfId="13"/>
     <tableColumn id="6" xr3:uid="{4D9AB0FD-D55E-403F-8BCA-580F18B60E69}" name="Costeo_Producto"/>
     <tableColumn id="7" xr3:uid="{C20B166E-89C9-437B-BE2F-0575CD9B61A3}" name="Producto"/>
     <tableColumn id="8" xr3:uid="{3BACFAF4-2DB8-4231-9D27-6F456AAB29F2}" name="Cliente"/>
     <tableColumn id="9" xr3:uid="{48527FED-A1C6-4451-980E-6C488A33B512}" name="Cantidad Solicitada"/>
     <tableColumn id="10" xr3:uid="{968D6B5C-CC57-4F65-A895-0A69BF2EED98}" name="Id."/>
-    <tableColumn id="11" xr3:uid="{F40E1C32-DE28-4FDD-89E6-E2A6493B478C}" name="Fecha" dataDxfId="13" totalsRowDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{DD9CAA1A-7A1B-4DC7-B289-2166158EBB0E}" name="costo_antes_iva" dataDxfId="12" totalsRowDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{F40E1C32-DE28-4FDD-89E6-E2A6493B478C}" name="Fecha" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{DD9CAA1A-7A1B-4DC7-B289-2166158EBB0E}" name="costo_antes_iva" dataDxfId="10" totalsRowDxfId="9"/>
     <tableColumn id="13" xr3:uid="{9E3415EA-575B-49D8-BB2A-C71677B7801C}" name="fecha_creacion"/>
     <tableColumn id="14" xr3:uid="{338E4A5E-8884-459D-8BCA-EFE8CB708CD4}" name="Proceso Producción"/>
     <tableColumn id="15" xr3:uid="{49B8C130-E821-43FC-B974-23ADC4B1861B}" name="OP-D"/>
-    <tableColumn id="16" xr3:uid="{32719A37-909D-482F-B8D5-0982780D41E3}" name="OS-Valor Unitario" dataDxfId="11" totalsRowDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{32719A37-909D-482F-B8D5-0982780D41E3}" name="OS-Valor Unitario" dataDxfId="8" totalsRowDxfId="7"/>
     <tableColumn id="17" xr3:uid="{F8561042-AEDD-49C3-A033-1A8155D26C69}" name="OS-Cantidad"/>
     <tableColumn id="18" xr3:uid="{494B13A6-4D96-407B-B396-A29E7B0B9A92}" name="Num OS"/>
     <tableColumn id="19" xr3:uid="{30579657-230D-4D20-9ECE-63B4892645D2}" name="Costeo"/>
     <tableColumn id="20" xr3:uid="{68D95147-9433-4572-A3BA-21A33FE46032}" name="Nombre"/>
     <tableColumn id="21" xr3:uid="{6F9B902D-DA3C-4952-BF23-0683B3B70FEC}" name="Nombre del Comercial"/>
-    <tableColumn id="22" xr3:uid="{8A3A2D1A-0453-457D-B0E3-37580DF8B25E}" name="Diferencia valor unitario" dataDxfId="10" totalsRowDxfId="2">
+    <tableColumn id="22" xr3:uid="{8A3A2D1A-0453-457D-B0E3-37580DF8B25E}" name="Diferencia valor unitario" dataDxfId="6" totalsRowDxfId="5">
       <calculatedColumnFormula>Tabla1[[#This Row],[OS-Valor Unitario]]-Tabla1[[#This Row],[costo_antes_iva]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{20F3EE98-B924-4B76-B8D2-E72048A617DD}" name="Valor total OS" dataDxfId="9">
+    <tableColumn id="23" xr3:uid="{20F3EE98-B924-4B76-B8D2-E72048A617DD}" name="Valor total OS" dataDxfId="4">
       <calculatedColumnFormula>Tabla1[[#This Row],[OS-Valor Unitario]]*Tabla1[[#This Row],[OS-Cantidad]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{5C8B4893-2939-4889-A46C-5A1A9193B1C1}" name="valor total op" dataDxfId="8" totalsRowDxfId="1">
+    <tableColumn id="24" xr3:uid="{5C8B4893-2939-4889-A46C-5A1A9193B1C1}" name="valor total op" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>Tabla1[[#This Row],[costo_antes_iva]]*Tabla1[[#This Row],[OS-Cantidad]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{D6207476-A701-4586-9103-2B3DC710D87B}" name="Diferencia" dataDxfId="7" totalsRowDxfId="0">
+    <tableColumn id="25" xr3:uid="{D6207476-A701-4586-9103-2B3DC710D87B}" name="Diferencia" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>Tabla1[[#This Row],[Valor total OS]]-Tabla1[[#This Row],[valor total op]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4983,7 +4983,7 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="6" t="s">
         <v>1446</v>
       </c>
       <c r="W1" s="6" t="s">
